--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/14,07,26 ПОКОМ КИ/дв 14,07,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/14,07,26 ПОКОМ КИ/дв 14,07,26 млрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\14,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F212DD-0EE6-4789-8069-D1A75F757D7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6003BEEE-1032-405C-ABC1-349458790340}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="253">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -788,6 +788,9 @@
   <si>
     <t>18,07,</t>
   </si>
+  <si>
+    <t>дн</t>
+  </si>
 </sst>
 </file>
 
@@ -1307,7 +1310,9 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -2025,7 +2030,7 @@
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="5">
-        <f t="shared" ref="S7:S70" si="8">R9</f>
+        <f t="shared" ref="S9:S70" si="8">R9</f>
         <v>0</v>
       </c>
       <c r="T9" s="1" t="e">
